--- a/Lasser_Driver_v5/AFE_Card/AFE_Card_BOM_digikey.xlsx
+++ b/Lasser_Driver_v5/AFE_Card/AFE_Card_BOM_digikey.xlsx
@@ -499,36 +499,36 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1729131</t>
+          <t>374144-E</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix Contact</t>
+          <t>TE Connectivity</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AFE_Card J202,J203</t>
+          <t>AFE_Card J1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MKDS 1,5/3-5,08</t>
+          <t>DIN41612 M 3x8+8</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TerminalBlock_MKDS_3_P5.08mm</t>
+          <t>DIN41612_M_3x8+8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3-pos PCB screw terminal 5.08mm side-entry, PD pigtail (J202/203); same as AC board</t>
+          <t>DIN41612 Type M 24sig+8pwr R/A male backplane conn (J1)</t>
         </is>
       </c>
     </row>
@@ -538,42 +538,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>374144-E</t>
+          <t>AD5696RARUZ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TE Connectivity</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AFE_Card J1</t>
+          <t>AFE_Card U206</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DIN41612 M 3x8+8</t>
+          <t>AD5696R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DIN41612_M_3x8+8</t>
+          <t>TSSOP-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DIN41612 Type M 24sig+8pwr R/A male backplane conn (J1)</t>
+          <t>Quad 16-bit I2C DAC at 0x0E (A1=VLOGIC,A0=GND), int 2.5V ref, GAIN=GND -&gt; 0..2.5V; automatic ERR offset null via R146/R147 (U206)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AD5696RARUZ</t>
+          <t>AD835ARZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -583,57 +583,57 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AFE_Card U206</t>
+          <t>AFE_Card U45,U46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AD5696R</t>
+          <t>AD835</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TSSOP-16</t>
+          <t>SOIC-8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Quad 16-bit I2C DAC at 0x0E (A1=VLOGIC,A0=GND), int 2.5V ref, GAIN=GND -&gt; 0..2.5V; automatic ERR offset null via R146/R147 (U206)</t>
+          <t>250MHz 4-quadrant multiplier, PDH demodulator (U45/46)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AD835ARZ</t>
+          <t>ADS1115IDGSR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AFE_Card U45,U46</t>
+          <t>AFE_Card U201</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AD835</t>
+          <t>ADS1115</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SOIC-8</t>
+          <t>VSSOP-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>250MHz 4-quadrant multiplier, PDH demodulator (U45/46)</t>
+          <t>16-bit 4ch I2C ADC at 0x4A (ADDR-&gt;SDA), differential PD level monitor (U201)</t>
         </is>
       </c>
     </row>
@@ -643,42 +643,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADS1115IDGSR</t>
+          <t>C0805C105K5RACTU</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Kemet</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AFE_Card U201</t>
+          <t>AFE_Card C241</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ADS1115</t>
+          <t>1uF</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>VSSOP-10</t>
+          <t>C_0805</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>16-bit 4ch I2C ADC at 0x4A (ADDR-&gt;SDA), differential PD level monitor (U201)</t>
+          <t>MLCC 1uF 50V X7R 0805 (VREF_MID local bulk)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C0805C105K5RACTU</t>
+          <t>C0805C106K3PACTU</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AFE_Card C241</t>
+          <t>AFE_Card C215,C223,C226,C228,C229,C231,C232,C242,C243,C252</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1uF</t>
+          <t>10uF</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -703,17 +703,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MLCC 1uF 50V X7R 0805 (VREF_MID local bulk)</t>
+          <t>MLCC 10uF 25V X5R 0805 (rail bulk +/-5V, +/-15V, I2C-3V3, VREF_TIA)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C0805C106K3PACTU</t>
+          <t>C0805C475K3RACTU</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AFE_Card C215,C223,C226,C228,C229,C231,C232,C242,C243,C244,C252</t>
+          <t>AFE_Card C1,C2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10uF</t>
+          <t>4.7uF</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MLCC 10uF 25V X5R 0805 (rail bulk +/-5V, +/-15V, I2C-3V3, VREF_TIA)</t>
+          <t>MLCC 4.7uF 25V X7R 0805 (LT3042 SET soft-start + output)</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C0805C475K3RACTU</t>
+          <t>C0805C680J5GACTU</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -758,12 +758,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AFE_Card C1,C2</t>
+          <t>AFE_Card C98,C99</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.7uF</t>
+          <t>68pF C0G</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MLCC 4.7uF 25V X7R 0805 (LT3042 SET soft-start + output)</t>
+          <t>MLCC 68pF 50V C0G 0805 (ERR stage 2nd pole, across Rf C98/99)</t>
         </is>
       </c>
     </row>
@@ -783,22 +783,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C0805C680J5GACTU</t>
+          <t>CL21B102KBANNNC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kemet</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AFE_Card C98,C99</t>
+          <t>AFE_Card C96,C97</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>68pF C0G</t>
+          <t>1nF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MLCC 68pF 50V C0G 0805 (ERR stage 2nd pole, across Rf C98/99)</t>
+          <t>MLCC 1nF 50V X7R 0805 (ERR filter 1st pole C96/97)</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CL21B102KBANNNC</t>
+          <t>CL21B103KBANNNC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -828,12 +828,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AFE_Card C96,C97</t>
+          <t>AFE_Card C94,C95</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1nF</t>
+          <t>10nF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MLCC 1nF 50V X7R 0805 (ERR filter 1st pole C96/97)</t>
+          <t>MLCC 10nF 50V X7R 0805 (TIA-&gt;mixer RF AC-couple C94/95)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CL21B103KBANNNC</t>
+          <t>CL21B104KBCNNNC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AFE_Card C94,C95</t>
+          <t>AFE_Card C213,C214,C216,C217,C218,C219,C220,C221,C222,C224,C225,C227,C230,C233,C234,C235,C236,C237,C238,C247,C248,C249,C250,C251,C253,C254,C255,C256,C_K1,C_K2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10nF</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -878,67 +878,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MLCC 10nF 50V X7R 0805 (TIA-&gt;mixer RF AC-couple C94/95)</t>
+          <t>MLCC 100nF 50V X7R 0805 (decoupling + coupling + PD level + VB bypass)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CL21B104KBCNNNC</t>
+          <t>CRCW08051K00FKEA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Vishay Dale</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AFE_Card C213,C214,C216,C217,C218,C219,C220,C221,C222,C224,C225,C227,C230,C233,C234,C235,C236,C237,C238,C239,C240,C245,C246,C247,C248,C249,C250,C251,C253,C254,C_K1,C_K2</t>
+          <t>AFE_Card R125,R128</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>100nF</t>
+          <t>1.00k</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C_0805</t>
+          <t>R_0805</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MLCC 100nF 50V X7R 0805 (decoupling + coupling + PD level + VB bypass)</t>
+          <t>Res 1.00k 1% 0805 (LO buffer Rg; Av=1+Rf/Rg=3)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CRCW08051K00FKEA</t>
+          <t>ERA-6AEB124V</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vishay Dale</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AFE_Card R125,R128</t>
+          <t>AFE_Card R2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.00k</t>
+          <t>120k 0.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Res 1.00k 1% 0805 (LO buffer Rg; Av=1+Rf/Rg=3)</t>
+          <t>Res 120k 0.1% 0805 (LT3042 SET -&gt; 12V PD bias)</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ERA-6AEB124V</t>
+          <t>ERJ-6ENF3573V</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AFE_Card R2</t>
+          <t>AFE_Card R144</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>120k 0.1%</t>
+          <t>357k</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -983,112 +983,112 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Res 120k 0.1% 0805 (LT3042 SET -&gt; 12V PD bias)</t>
+          <t>Res 357k 1% 0805 (LT3042 PGFB divider top; PG trips at 11.0V)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ERJ-6ENF3573V</t>
+          <t>GRM1555C1H1R0CA01D</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Panasonic</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AFE_Card R144</t>
+          <t>AFE_Card C78,C79</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>357k</t>
+          <t>1pF C0G</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R_0805</t>
+          <t>C_0402</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Res 357k 1% 0805 (LT3042 PGFB divider top; PG trips at 11.0V)</t>
+          <t>MLCC 1.0pF 50V C0G 0402 (TIA feedback Cf C78/79)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GRM1555C1H1R0CA01D</t>
+          <t>LT3042EMSE#PBF</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AFE_Card C78,C79</t>
+          <t>AFE_Card U1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1pF C0G</t>
+          <t>LT3042</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C_0402</t>
+          <t>MSOP-10-EP</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MLCC 1.0pF 50V C0G 0402 (TIA feedback Cf C78/79)</t>
+          <t>Ultralow-noise LDO, SET=120k-&gt;12V PD bias (U1)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LT3042EMSE#PBF</t>
+          <t>OPA192IDBVR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AFE_Card U1</t>
+          <t>AFE_Card U202,U203</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LT3042</t>
+          <t>OPA192</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MSOP-12-EP</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ultralow-noise LDO, SET=120k-&gt;12V PD bias (U1)</t>
+          <t>Precision op-amp, ERR inverting x5.02 level-shift output stage (U202/203)</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OPA192IDBVR</t>
+          <t>OPA814DBVR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AFE_Card U202,U203</t>
+          <t>AFE_Card U30,U31</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OPA192</t>
+          <t>OPA814</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Precision op-amp, ERR inverting x4.99 level-shift output stage (U202/203)</t>
+          <t>250MHz GBW JFET-input op-amp, PD transimpedance TIA (U30/31). Ground-referenced on +/-5V: the +/-5V CM ceiling is +2.1V so the old 3.336V VREF_TIA was out of range</t>
         </is>
       </c>
     </row>
@@ -1168,42 +1168,42 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OPA859IDSGR</t>
+          <t>RC0805FR-07100KL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AFE_Card U30,U31</t>
+          <t>AFE_Card R146,R147</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OPA859</t>
+          <t>100k</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SON-8</t>
+          <t>R_0805</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.8GHz unity-gain-stable (compensated) FET-input amp, PD transimpedance TIA (U30/31)</t>
+          <t>Res 100k 1% 0805 (VREF_TIA bottom leg -&gt; 3.336V TIA reference)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RC0805FR-07100KL</t>
+          <t>RC0805FR-07100RL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AFE_Card R133,R146,R147</t>
+          <t>AFE_Card R211,R212,R_S1,R_S2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>100R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Res 100k 1% 0805 (VREF_TIA bottom leg -&gt; 3.336V TIA reference)</t>
+          <t>Res 100R 1% 0805 (I2C series R211/212; VREF_TIA RC R130/131; PD bias R_S1/2)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RC0805FR-07100RL</t>
+          <t>RC0805FR-0710KL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AFE_Card R130,R131,R211,R212,R_S1,R_S2</t>
+          <t>AFE_Card R120,R121,R122,R123,R126,R129,R134,R135,R145,R213,R214</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>100R</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Res 100R 1% 0805 (I2C series R211/212; VREF_TIA RC R130/131; PD bias R_S1/2)</t>
+          <t>Res 10k 1% 0805 (AD835 X/Y bias, LO bias, ADC dividers, PG bot)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RC0805FR-0710KL</t>
+          <t>RC0805FR-0710RL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AFE_Card R118,R119,R120,R121,R122,R123,R126,R129,R134,R135,R136,R137,R145,R213,R214</t>
+          <t>AFE_Card R216</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>10R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1298,17 +1298,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Res 10k 1% 0805 (AD835 X/Y bias, LO bias, ERR stage Ri, ADC dividers, PG bot)</t>
+          <t>Res 10R 1% 0805 (I2C-3V3 filter R216)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RC0805FR-0710RL</t>
+          <t>RC0805FR-072KL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AFE_Card R216</t>
+          <t>AFE_Card R124,R127</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10R</t>
+          <t>2.00k</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Res 10R 1% 0805 (I2C-3V3 filter R216)</t>
+          <t>Res 2.00k 1% 0805 (LO buffer Rf, gain set)</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RC0805FR-072KL</t>
+          <t>RC0805FR-073K3L</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AFE_Card R124,R127</t>
+          <t>AFE_Card R116,R117</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2.00k</t>
+          <t>3.3k</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Res 2.00k 1% 0805 (LO buffer Rf, gain set)</t>
+          <t>Res 3.3k 1% 0805 (ERR filter 1st pole R116/117; also the upper half of the ERR stage Ri = 3.3k+6.65k = 9.95k)</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RC0805FR-073K3L</t>
+          <t>RC0805FR-0747RL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AFE_Card R116,R117</t>
+          <t>AFE_Card R217,R218</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3.3k</t>
+          <t>47R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Res 3.3k 1% 0805 (ERR filter 1st pole R116/117)</t>
+          <t>Res 47R 1% 0805 (ERR bus series R217/218)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RC0805FR-0747RL</t>
+          <t>RC0805FR-0749K9L</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AFE_Card R217,R218</t>
+          <t>AFE_Card R138,R139,R140,R142</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>47R</t>
+          <t>49.9k</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Res 47R 1% 0805 (ERR bus series R217/218)</t>
+          <t>Res 49.9k 1% 0805 (ERR stage Rf R138/139 -&gt; Av=-5.02 into Ri=9.95k; VB dividers)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RC0805FR-0749K9L</t>
+          <t>RC0805FR-076K04L</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AFE_Card R132,R138,R139,R140,R142</t>
+          <t>AFE_Card R1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>49.9k</t>
+          <t>6.04k</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Res 49.9k 1% 0805 (ERR stage Rf R138/139 -&gt; Av=-4.99; VREF_TIA top; VB dividers)</t>
+          <t>Res 6.04k 1% 0805 (LT3042 ILIM ~21mA)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RC0805FR-076K04L</t>
+          <t>RC0805FR-076K65L</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AFE_Card R1</t>
+          <t>AFE_Card R118,R119</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6.04k</t>
+          <t>6.65k</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Res 6.04k 1% 0805 (LT3042 ILIM ~21mA)</t>
+          <t>Res 6.65k 1% 0805 (ERR stage Ri lower half R118/119; C96/97 shunt the R116/R118 junction to GND so both are in the DC path - 10k here would give Av=-3.75 and put 2.500V out of null range)</t>
         </is>
       </c>
     </row>
